--- a/Zinc/5. Statistical data analysis/Multiple linear regression plots/MLR_summary_table.xlsx
+++ b/Zinc/5. Statistical data analysis/Multiple linear regression plots/MLR_summary_table.xlsx
@@ -1,91 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/5. Statistical data analysis/Multiple linear regression plots/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEC6933B00A9E6D224D522D233FC1993925979E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBF16CE9-1286-416B-9B20-D9A33259F35C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
-    <t xml:space="preserve">Term</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Std. Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pr(&gt;|t|)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Ca_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cl_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_K_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Mg_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Na_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_SO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Temp_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual standard error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple R-squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted R-squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p-value</t>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Std. Error</t>
+  </si>
+  <si>
+    <t>t value</t>
+  </si>
+  <si>
+    <t>Pr(&gt;|t|)</t>
+  </si>
+  <si>
+    <t>VIF</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>log_Ca_uM</t>
+  </si>
+  <si>
+    <t>log_Cl_uM</t>
+  </si>
+  <si>
+    <t>log_DOC_uM</t>
+  </si>
+  <si>
+    <t>log_K_uM</t>
+  </si>
+  <si>
+    <t>log_Mg_uM</t>
+  </si>
+  <si>
+    <t>log_Na_uM</t>
+  </si>
+  <si>
+    <t>log_SO4_uM</t>
+  </si>
+  <si>
+    <t>log_Temp_C</t>
+  </si>
+  <si>
+    <t>log_Zn_uM</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>Residual standard error</t>
+  </si>
+  <si>
+    <t>Multiple R-squared</t>
+  </si>
+  <si>
+    <t>Adjusted R-squared</t>
+  </si>
+  <si>
+    <t>F-statistic</t>
+  </si>
+  <si>
+    <t>p-value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -121,6 +128,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -402,11 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -426,286 +442,265 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="n">
-        <v>-0.000000000000000959682335433058</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.012801519919626</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.0000000000000749662806806067</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.99999999999994</v>
-      </c>
-      <c r="F2"/>
-    </row>
-    <row r="3">
+      <c r="B2">
+        <v>-9.5968233543305803E-16</v>
+      </c>
+      <c r="C2">
+        <v>1.2801519919625999E-2</v>
+      </c>
+      <c r="D2">
+        <v>-7.4966280680606706E-14</v>
+      </c>
+      <c r="E2">
+        <v>0.99999999999994005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="n">
-        <v>-0.443184017220205</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0243879225123455</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-18.1722742884663</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000222205803664585</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.61992827149766</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3">
+        <v>-0.44318401722020501</v>
+      </c>
+      <c r="C3">
+        <v>2.4387922512345499E-2</v>
+      </c>
+      <c r="D3">
+        <v>-18.172274288466301</v>
+      </c>
+      <c r="E3">
+        <v>2.2220580366458499E-53</v>
+      </c>
+      <c r="F3">
+        <v>3.6199282714976602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="n">
-        <v>-0.179110025538273</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0398539405445971</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-4.49416100618324</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.00000931864218030835</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9.66702605941339</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4">
+        <v>-0.17911002553827299</v>
+      </c>
+      <c r="C4">
+        <v>3.9853940544597101E-2</v>
+      </c>
+      <c r="D4">
+        <v>-4.4941610061832398</v>
+      </c>
+      <c r="E4">
+        <v>9.3186421803083498E-6</v>
+      </c>
+      <c r="F4">
+        <v>9.6670260594133897</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="n">
-        <v>-0.430289904357391</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0201785569134535</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-21.3241167940264</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000119036493915174</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.47816694773436</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5">
+        <v>-0.43028990435739101</v>
+      </c>
+      <c r="C5">
+        <v>2.0178556913453501E-2</v>
+      </c>
+      <c r="D5">
+        <v>-21.324116794026398</v>
+      </c>
+      <c r="E5">
+        <v>1.19036493915174E-66</v>
+      </c>
+      <c r="F5">
+        <v>2.4781669477343602</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>-0.115783935942082</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.0259434454151166</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>2.59434454151166E-2</v>
+      </c>
+      <c r="D6">
         <v>-4.46293597821892</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.0000107061006721183</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.09643111434602</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="E6">
+        <v>1.07061006721183E-5</v>
+      </c>
+      <c r="F6">
+        <v>4.0964311143460197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.0369000517856305</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0263099027265817</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="B7">
+        <v>3.6900051785630501E-2</v>
+      </c>
+      <c r="C7">
+        <v>2.6309902726581701E-2</v>
+      </c>
+      <c r="D7">
         <v>1.40251570555407</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.161588605048647</v>
       </c>
-      <c r="F7" t="n">
-        <v>4.2129745633162</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="F7">
+        <v>4.2129745633161999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.187327963501056</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0512947278776543</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="B8">
+        <v>0.18732796350105599</v>
+      </c>
+      <c r="C8">
+        <v>5.1294727877654302E-2</v>
+      </c>
+      <c r="D8">
         <v>3.65199253903562</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.000297201966351537</v>
-      </c>
-      <c r="F8" t="n">
-        <v>16.013852078365</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="E8">
+        <v>2.9720196635153701E-4</v>
+      </c>
+      <c r="F8">
+        <v>16.013852078365002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.0545320923307553</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0250485233688588</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9">
+        <v>5.4532092330755302E-2</v>
+      </c>
+      <c r="C9">
+        <v>2.5048523368858801E-2</v>
+      </c>
+      <c r="D9">
         <v>2.17705816537479</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.0300993032838911</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.81869181253182</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="E9">
+        <v>3.0099303283891099E-2</v>
+      </c>
+      <c r="F9">
+        <v>3.8186918125318199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="n">
-        <v>-0.0556759848285464</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0137604025809651</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-4.04610144950001</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0000632625709913899</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.15242489698423</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="B10">
+        <v>-5.5675984828546403E-2</v>
+      </c>
+      <c r="C10">
+        <v>1.37604025809651E-2</v>
+      </c>
+      <c r="D10">
+        <v>-4.0461014495000098</v>
+      </c>
+      <c r="E10">
+        <v>6.3262570991389904E-5</v>
+      </c>
+      <c r="F10">
+        <v>1.1524248969842299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="n">
-        <v>0.909053647935369</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.0158020404075683</v>
-      </c>
-      <c r="D11" t="n">
-        <v>57.5276119089016</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000375256425259233</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.51976587358556</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="B11">
+        <v>0.90905364793536902</v>
+      </c>
+      <c r="C11">
+        <v>1.5802040407568298E-2</v>
+      </c>
+      <c r="D11">
+        <v>57.527611908901598</v>
+      </c>
+      <c r="E11">
+        <v>3.75256425259233E-188</v>
+      </c>
+      <c r="F11">
+        <v>1.5197658735855599</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>0.141975490651402</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.0150200942588509</v>
-      </c>
-      <c r="D12" t="n">
-        <v>9.45237015192098</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.000000000000000000367808469070495</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="C12">
+        <v>1.50200942588509E-2</v>
+      </c>
+      <c r="D12">
+        <v>9.4523701519209808</v>
+      </c>
+      <c r="E12">
+        <v>3.67808469070495E-19</v>
+      </c>
+      <c r="F12">
         <v>1.37307945312407</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="n">
-        <v>0.251509960298784</v>
-      </c>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-    </row>
-    <row r="14">
+      <c r="B13">
+        <v>0.25150996029878397</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>0.938385785588153</v>
       </c>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-    </row>
-    <row r="15">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" t="n">
-        <v>0.936742739870504</v>
-      </c>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-    </row>
-    <row r="16">
+      <c r="B15">
+        <v>0.93674273987050405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>20</v>
       </c>
-      <c r="B16" t="n">
-        <v>571.12579127179</v>
-      </c>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-    </row>
-    <row r="17">
+      <c r="B16">
+        <v>571.12579127179004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" t="n">
-        <v>4.89864252162581e-220</v>
-      </c>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
+      <c r="B17">
+        <v>4.8986425216258099E-220</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>